--- a/diseases/d205/2005-2009.xlsx
+++ b/diseases/d205/2005-2009.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>4</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.07624737851981726</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>5</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.09530922314977158</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>4</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.07624737851981726</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>1</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -6309,9 +6267,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6705,9 +6660,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -7101,9 +7053,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -7497,9 +7446,6 @@
       <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -7893,9 +7839,6 @@
       <c r="O38" t="n">
         <v>4</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.07595542669717416</v>
       </c>
@@ -8289,9 +8232,6 @@
       <c r="O40" t="n">
         <v>3</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.05696657002288063</v>
       </c>
@@ -8685,9 +8625,6 @@
       <c r="O42" t="n">
         <v>4</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.07595542669717416</v>
       </c>
@@ -9081,9 +9018,6 @@
       <c r="O44" t="n">
         <v>6</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.1139331400457613</v>
       </c>
@@ -9477,9 +9411,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -9873,9 +9804,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -10269,9 +10197,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -10665,9 +10590,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -11061,9 +10983,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -11457,9 +11376,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -11853,9 +11769,6 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -12249,9 +12162,6 @@
       <c r="O60" t="n">
         <v>5</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.09454101283677872</v>
       </c>
@@ -12645,9 +12555,6 @@
       <c r="O62" t="n">
         <v>4</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.07563281026942298</v>
       </c>
@@ -13041,9 +12948,6 @@
       <c r="O64" t="n">
         <v>4</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.07563281026942298</v>
       </c>
@@ -13437,9 +13341,6 @@
       <c r="O66" t="n">
         <v>4</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.07563281026942298</v>
       </c>
@@ -13833,9 +13734,6 @@
       <c r="O68" t="n">
         <v>2</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -14229,9 +14127,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -14625,9 +14520,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -15021,9 +14913,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -15417,9 +15306,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -15813,9 +15699,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -16209,9 +16092,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -16605,9 +16485,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -17001,9 +16878,6 @@
       <c r="O84" t="n">
         <v>1</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -17397,9 +17271,6 @@
       <c r="O86" t="n">
         <v>6</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.1129225349528181</v>
       </c>
@@ -17793,9 +17664,6 @@
       <c r="O88" t="n">
         <v>8</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.1505633799370908</v>
       </c>
@@ -18189,9 +18057,6 @@
       <c r="O90" t="n">
         <v>5</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.09410211246068179</v>
       </c>
@@ -18585,9 +18450,6 @@
       <c r="O92" t="n">
         <v>2</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.03764084498427271</v>
       </c>
@@ -18981,9 +18843,6 @@
       <c r="O94" t="n">
         <v>1</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -19377,9 +19236,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -19773,9 +19629,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -20169,9 +20022,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -20565,9 +20415,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -20961,9 +20808,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -21357,9 +21201,6 @@
       <c r="O106" t="n">
         <v>1</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -21753,9 +21594,6 @@
       <c r="O108" t="n">
         <v>2</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.03746120540981013</v>
       </c>
@@ -22149,9 +21987,6 @@
       <c r="O110" t="n">
         <v>8</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.1498448216392405</v>
       </c>
@@ -22545,9 +22380,6 @@
       <c r="O112" t="n">
         <v>7</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.1311142189343355</v>
       </c>
@@ -22941,9 +22773,6 @@
       <c r="O114" t="n">
         <v>3</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.0561918081147152</v>
       </c>
@@ -23337,9 +23166,6 @@
       <c r="O116" t="n">
         <v>1</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -23733,9 +23559,6 @@
       <c r="O118" t="n">
         <v>2</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.03746120540981013</v>
       </c>
@@ -24128,9 +23951,6 @@
       </c>
       <c r="O120" t="n">
         <v>1</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>0.01873060270490507</v>

--- a/diseases/d205/2005-2009.xlsx
+++ b/diseases/d205/2005-2009.xlsx
@@ -10546,12 +10546,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2007-02-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2007-02</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_GR_ECDC_TBE_ANNUAL</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_GR_ECDC_TBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT52" t="n">
@@ -10633,47 +10633,47 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -10705,12 +10705,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -10735,12 +10735,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2007-02-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2007-02</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -10751,22 +10751,22 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_GR_ECDC_TBE_ANNUAL</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_GR_ECDC_TBE_ANNUAL</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_GR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>TBE (tick borne encephalitis)</t>
+          <t>Tick-borne encephalitis</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:GR:national</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
@@ -10826,17 +10826,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
+          <t>Greece annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -10854,12 +10854,12 @@
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_GR_ECDC_TBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT53" t="n">
@@ -10867,47 +10867,47 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -10969,12 +10969,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2007-03-01</t>
+          <t>2007-02-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2007-03</t>
+          <t>2007-02</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -11128,12 +11128,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2007-03-01</t>
+          <t>2007-02-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2007-03</t>
+          <t>2007-02</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -11362,12 +11362,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2007-04-01</t>
+          <t>2007-03-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2007-04</t>
+          <t>2007-03</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -11521,12 +11521,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2007-04-01</t>
+          <t>2007-03-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2007-04</t>
+          <t>2007-03</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -11755,22 +11755,22 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2007-05-01</t>
+          <t>2007-04-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2007-05</t>
+          <t>2007-04</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.01890820256735574</v>
+        <v>0</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -11914,19 +11914,19 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2007-05-01</t>
+          <t>2007-04-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2007-05</t>
+          <t>2007-04</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -12148,22 +12148,22 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
+          <t>2007-05-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2007-06</t>
+          <t>2007-05</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>0.09454101283677872</v>
+        <v>0.01890820256735574</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -12307,19 +12307,19 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
+          <t>2007-05-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2007-06</t>
+          <t>2007-05</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -12541,22 +12541,22 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2007-07-01</t>
+          <t>2007-06-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2007-07</t>
+          <t>2007-06</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R62" t="n">
-        <v>0.07563281026942298</v>
+        <v>0.09454101283677872</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -12700,19 +12700,19 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2007-07-01</t>
+          <t>2007-06-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2007-07</t>
+          <t>2007-06</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -12934,12 +12934,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2007-08-01</t>
+          <t>2007-07-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2007-08</t>
+          <t>2007-07</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2007-08-01</t>
+          <t>2007-07-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2007-08</t>
+          <t>2007-07</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -13327,12 +13327,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2007-09-01</t>
+          <t>2007-08-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2007-09</t>
+          <t>2007-08</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -13486,12 +13486,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2007-09-01</t>
+          <t>2007-08-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2007-09</t>
+          <t>2007-08</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -13720,22 +13720,22 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2007-10-01</t>
+          <t>2007-09-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2007-10</t>
+          <t>2007-09</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R68" t="n">
-        <v>0.03781640513471149</v>
+        <v>0.07563281026942298</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -13879,19 +13879,19 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2007-10-01</t>
+          <t>2007-09-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2007-10</t>
+          <t>2007-09</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -14113,22 +14113,22 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2007-11-01</t>
+          <t>2007-10-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2007-11</t>
+          <t>2007-10</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>0.03781640513471149</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -14272,19 +14272,19 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2007-11-01</t>
+          <t>2007-10-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2007-11</t>
+          <t>2007-10</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -14506,12 +14506,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-11-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2007-12</t>
+          <t>2007-11</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -14665,12 +14665,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-11-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2007-12</t>
+          <t>2007-11</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -14899,12 +14899,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-12-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-12</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -15058,12 +15058,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-12-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-12</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -15292,12 +15292,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2008-02-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -15451,12 +15451,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2008-02-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -15655,12 +15655,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -15685,12 +15685,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2008-03-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N78" t="n">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_GR_ECDC_TBE_ANNUAL</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -15729,12 +15729,12 @@
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_GR_ECDC_TBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT78" t="n">
@@ -15742,47 +15742,47 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -15814,12 +15814,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -15844,12 +15844,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2008-03-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -15860,22 +15860,22 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_GR_ECDC_TBE_ANNUAL</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_GR_ECDC_TBE_ANNUAL</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_GR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>TBE (tick borne encephalitis)</t>
+          <t>Tick-borne encephalitis</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:GR:national</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr">
@@ -15935,17 +15935,17 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
+          <t>Greece annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -15963,12 +15963,12 @@
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_GR_ECDC_TBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT79" t="n">
@@ -15976,47 +15976,47 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -16078,12 +16078,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2008-04-01</t>
+          <t>2008-02-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -16237,12 +16237,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2008-04-01</t>
+          <t>2008-02-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -16471,12 +16471,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2008-03-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -16630,12 +16630,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2008-03-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="N83" t="n">
@@ -16864,22 +16864,22 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2008-04-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>0.01882042249213636</v>
+        <v>0</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -17023,19 +17023,19 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2008-04-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -17257,22 +17257,22 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="N86" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0.1129225349528181</v>
+        <v>0</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -17416,19 +17416,19 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -17650,22 +17650,22 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O88" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R88" t="n">
-        <v>0.1505633799370908</v>
+        <v>0.01882042249213636</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -17809,19 +17809,19 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O89" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -18043,22 +18043,22 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R90" t="n">
-        <v>0.09410211246068179</v>
+        <v>0.1129225349528181</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -18202,19 +18202,19 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -18436,22 +18436,22 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O92" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R92" t="n">
-        <v>0.03764084498427271</v>
+        <v>0.1505633799370908</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -18595,19 +18595,19 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O93" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -18829,22 +18829,22 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O94" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R94" t="n">
-        <v>0.01882042249213636</v>
+        <v>0.09410211246068179</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -18988,19 +18988,19 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -19222,22 +19222,22 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>0.03764084498427271</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -19381,19 +19381,19 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -19615,22 +19615,22 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>0.01882042249213636</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -19774,19 +19774,19 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -20008,12 +20008,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N100" t="n">
@@ -20167,12 +20167,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N101" t="n">
@@ -20401,12 +20401,12 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N102" t="n">
@@ -20560,12 +20560,12 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N103" t="n">
@@ -20764,12 +20764,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -20794,12 +20794,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N104" t="n">
@@ -20818,12 +20818,12 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_GR_ECDC_TBE_ANNUAL</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -20838,12 +20838,12 @@
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_GR_ECDC_TBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT104" t="n">
@@ -20851,47 +20851,47 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -20923,12 +20923,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -20953,12 +20953,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N105" t="n">
@@ -20969,22 +20969,22 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_GR_ECDC_TBE_ANNUAL</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_GR_ECDC_TBE_ANNUAL</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_GR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>TBE (tick borne encephalitis)</t>
+          <t>Tick-borne encephalitis</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
@@ -20994,12 +20994,12 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
@@ -21009,7 +21009,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:GR:national</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr">
@@ -21044,17 +21044,17 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
+          <t>Greece annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21072,12 +21072,12 @@
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_GR_ECDC_TBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT105" t="n">
@@ -21085,47 +21085,47 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -21187,22 +21187,22 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>0.01873060270490507</v>
+        <v>0</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -21346,19 +21346,19 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
@@ -21580,22 +21580,22 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>0.03746120540981013</v>
+        <v>0</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -21739,19 +21739,19 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -21973,22 +21973,22 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>0.1498448216392405</v>
+        <v>0</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -22132,19 +22132,19 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N111" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -22366,22 +22366,22 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N112" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O112" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>0.1311142189343355</v>
+        <v>0.01873060270490507</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -22525,19 +22525,19 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N113" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O113" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
@@ -22759,22 +22759,22 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R114" t="n">
-        <v>0.0561918081147152</v>
+        <v>0.03746120540981013</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -22918,19 +22918,19 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -23152,22 +23152,22 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O116" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R116" t="n">
-        <v>0.01873060270490507</v>
+        <v>0.1498448216392405</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -23311,19 +23311,19 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O117" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
@@ -23545,22 +23545,22 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O118" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R118" t="n">
-        <v>0.03746120540981013</v>
+        <v>0.1311142189343355</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -23704,19 +23704,19 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O119" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -23938,22 +23938,22 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R120" t="n">
-        <v>0.01873060270490507</v>
+        <v>0.0561918081147152</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -24097,19 +24097,19 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -24268,6 +24268,1185 @@
         </is>
       </c>
       <c r="BC121" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" t="n">
+        <v>1</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.01873060270490507</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>1</v>
+      </c>
+      <c r="O123" t="n">
+        <v>1</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>TBE (tick borne encephalitis)</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AT123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>2</v>
+      </c>
+      <c r="O124" t="n">
+        <v>2</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.03746120540981013</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>2</v>
+      </c>
+      <c r="O125" t="n">
+        <v>2</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>TBE (tick borne encephalitis)</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN125" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" t="n">
+        <v>1</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.01873060270490507</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>1</v>
+      </c>
+      <c r="O127" t="n">
+        <v>1</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>TBE (tick borne encephalitis)</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -24389,7 +25568,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -24399,7 +25578,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">
@@ -24419,7 +25598,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -24429,7 +25608,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
